--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-09T07:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:17:44+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,6 +293,9 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -376,7 +379,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -434,6 +437,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -474,7 +481,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -554,7 +561,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -587,7 +594,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -679,72 +686,72 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -772,7 +779,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
 </t>
   </si>
   <si>
@@ -813,7 +820,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -871,7 +878,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -915,7 +922,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -968,7 +975,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1057,10 +1064,7 @@
     <t>If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.3.0</t>
   </si>
   <si>
     <t>Quantity.comparator</t>
@@ -1249,13 +1253,13 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1375,7 +1379,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1541,7 +1545,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1563,7 +1567,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1578,10 +1582,14 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1631,7 +1639,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2264,7 +2272,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2272,10 +2280,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2286,7 +2294,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>82</v>
@@ -2295,19 +2303,19 @@
         <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2357,13 +2365,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2392,10 +2400,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2406,7 +2414,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>82</v>
@@ -2415,16 +2423,16 @@
         <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2475,19 +2483,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2510,10 +2518,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2524,28 +2532,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2595,19 +2603,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2630,10 +2638,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2644,7 +2652,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2656,16 +2664,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2691,13 +2699,13 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>82</v>
@@ -2715,19 +2723,19 @@
         <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2750,21 +2758,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2776,16 +2784,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2835,19 +2843,19 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
@@ -2859,7 +2867,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2870,14 +2878,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2896,16 +2904,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2955,7 +2963,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2967,7 +2975,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2979,7 +2987,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2990,14 +2998,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3016,16 +3024,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3075,7 +3083,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3087,7 +3095,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -3099,7 +3107,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3110,14 +3118,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3130,25 +3138,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3197,7 +3205,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3209,7 +3217,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3221,7 +3229,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3232,10 +3240,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3255,20 +3263,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3317,7 +3325,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3329,22 +3337,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3352,14 +3360,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3375,20 +3383,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3437,7 +3445,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3449,19 +3457,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3472,14 +3480,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3495,19 +3503,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3557,7 +3565,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3569,19 +3577,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3592,10 +3600,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3603,34 +3611,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3655,13 +3663,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3679,34 +3687,34 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3714,10 +3722,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3740,19 +3748,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3777,13 +3785,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3801,7 +3809,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3813,7 +3821,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3825,10 +3833,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3836,21 +3844,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3859,22 +3867,22 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3899,11 +3907,11 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3921,45 +3929,45 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3970,7 +3978,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3982,13 +3990,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>213</v>
+        <v>95</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4039,13 +4047,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -4063,7 +4071,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4074,14 +4082,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4100,16 +4108,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4147,19 +4155,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4171,7 +4179,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4183,7 +4191,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4194,10 +4202,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4217,22 +4225,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4281,7 +4289,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4293,7 +4301,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4302,10 +4310,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4316,10 +4324,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4330,7 +4338,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4339,22 +4347,22 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4364,7 +4372,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4403,19 +4411,19 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4424,10 +4432,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4438,10 +4446,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4449,10 +4457,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4461,22 +4469,22 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4525,34 +4533,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4560,10 +4568,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4583,19 +4591,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4645,7 +4653,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4657,7 +4665,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4666,13 +4674,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4680,21 +4688,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4703,22 +4711,22 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4767,34 +4775,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4802,21 +4810,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4825,22 +4833,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4877,44 +4885,44 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4922,23 +4930,23 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4947,22 +4955,22 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5011,34 +5019,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5046,10 +5054,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5060,7 +5068,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5069,19 +5077,19 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5131,19 +5139,19 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5152,13 +5160,13 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5166,10 +5174,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5177,7 +5185,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>81</v>
@@ -5189,20 +5197,20 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5251,7 +5259,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5263,22 +5271,22 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5286,10 +5294,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5297,10 +5305,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5309,22 +5317,22 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5361,68 +5369,68 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5431,22 +5439,22 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5495,45 +5503,45 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5544,7 +5552,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5556,13 +5564,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>213</v>
+        <v>95</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5613,13 +5621,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5637,7 +5645,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5648,14 +5656,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5674,16 +5682,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5721,19 +5729,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5745,7 +5753,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5757,7 +5765,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5768,10 +5776,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5779,10 +5787,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5791,22 +5799,22 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5855,19 +5863,19 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5876,10 +5884,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5890,10 +5898,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5904,35 +5912,35 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="R33" t="s" s="2">
         <v>82</v>
@@ -5953,13 +5961,11 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5977,19 +5983,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5998,10 +6004,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6012,10 +6018,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6026,7 +6032,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6035,20 +6041,20 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6097,19 +6103,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6118,10 +6124,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6132,10 +6138,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6146,7 +6152,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6155,20 +6161,20 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6217,19 +6223,19 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6238,10 +6244,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6252,10 +6258,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6266,7 +6272,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6275,22 +6281,22 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6339,19 +6345,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6360,10 +6366,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6374,10 +6380,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6388,7 +6394,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6400,19 +6406,19 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6437,13 +6443,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6461,19 +6467,19 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6482,10 +6488,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6496,14 +6502,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6522,19 +6528,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6559,13 +6565,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6583,7 +6589,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6595,33 +6601,33 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6635,7 +6641,7 @@
         <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6644,19 +6650,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6705,7 +6711,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6717,7 +6723,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6726,10 +6732,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6740,10 +6746,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6754,7 +6760,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6766,16 +6772,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6801,13 +6807,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6825,45 +6831,45 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6874,7 +6880,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6886,19 +6892,19 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6923,13 +6929,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6947,19 +6953,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6968,10 +6974,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6982,10 +6988,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6996,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7008,16 +7014,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7067,45 +7073,45 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7116,7 +7122,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7128,16 +7134,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7187,45 +7193,45 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7248,19 +7254,19 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7309,7 +7315,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7321,7 +7327,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7330,10 +7336,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7344,10 +7350,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7358,7 +7364,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7370,13 +7376,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7427,13 +7433,13 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7451,7 +7457,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7462,14 +7468,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7488,16 +7494,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7547,7 +7553,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7559,7 +7565,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7571,7 +7577,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7582,14 +7588,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7602,25 +7608,25 @@
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7669,7 +7675,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7681,7 +7687,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7693,7 +7699,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7704,10 +7710,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7718,7 +7724,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7730,13 +7736,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7787,19 +7793,19 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7808,10 +7814,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7822,10 +7828,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7836,7 +7842,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7848,13 +7854,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7905,19 +7911,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7926,10 +7932,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7940,10 +7946,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7954,7 +7960,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7966,19 +7972,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8003,13 +8009,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8027,31 +8033,31 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8062,10 +8068,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8088,19 +8094,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8125,13 +8131,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8149,7 +8155,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8161,19 +8167,19 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8184,10 +8190,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8198,7 +8204,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8210,17 +8216,17 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8269,19 +8275,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8293,7 +8299,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8304,10 +8310,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8318,7 +8324,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8330,13 +8336,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8387,19 +8393,19 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8408,10 +8414,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8422,10 +8428,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8445,19 +8451,19 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8507,7 +8513,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8519,7 +8525,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8528,10 +8534,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8542,10 +8548,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8553,10 +8559,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8565,19 +8571,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8627,7 +8633,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8639,7 +8645,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8648,10 +8654,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8662,10 +8668,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8685,22 +8691,22 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8749,7 +8755,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8761,7 +8767,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>503</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8770,10 +8776,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8784,10 +8790,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8798,7 +8804,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8810,13 +8816,13 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8867,13 +8873,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -8891,7 +8897,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8902,14 +8908,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8928,16 +8934,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8987,7 +8993,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8999,7 +9005,7 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9011,7 +9017,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9022,14 +9028,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9042,25 +9048,25 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9109,7 +9115,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9121,7 +9127,7 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9133,7 +9139,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9144,10 +9150,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9155,10 +9161,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9167,22 +9173,22 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9207,13 +9213,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9231,34 +9237,34 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9266,10 +9272,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9280,7 +9286,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9289,22 +9295,22 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9353,45 +9359,45 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9402,7 +9408,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9414,19 +9420,19 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9451,13 +9457,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9475,19 +9481,19 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9496,10 +9502,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9510,14 +9516,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9536,19 +9542,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9573,13 +9579,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9597,7 +9603,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9609,33 +9615,33 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9661,16 +9667,16 @@
         <v>83</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9719,7 +9725,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9731,7 +9737,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9740,10 +9746,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="527">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,9 +293,6 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>clinical.diagnostics</t>
-  </si>
-  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -379,7 +376,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -437,10 +434,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -481,7 +474,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -561,7 +554,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -594,7 +587,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -686,6 +679,10 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -748,10 +745,6 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -779,7 +772,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -820,7 +813,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -878,7 +871,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -922,7 +915,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -975,7 +968,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1064,7 +1057,10 @@
     <t>If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.3.0</t>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
   </si>
   <si>
     <t>Quantity.comparator</t>
@@ -1253,13 +1249,13 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1379,7 +1375,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1545,7 +1541,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1567,7 +1563,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1582,14 +1578,10 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1639,7 +1631,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2272,7 +2264,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2280,10 +2272,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2294,28 +2286,28 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2365,13 +2357,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2400,10 +2392,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2414,25 +2406,25 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2483,19 +2475,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2518,10 +2510,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2532,28 +2524,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2603,19 +2595,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2638,10 +2630,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2652,7 +2644,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2664,16 +2656,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2699,43 +2691,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2758,21 +2750,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2784,16 +2776,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2843,31 +2835,31 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2878,14 +2870,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2904,16 +2896,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2963,7 +2955,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2975,7 +2967,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2987,7 +2979,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2998,14 +2990,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3024,16 +3016,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3083,7 +3075,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3095,7 +3087,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -3107,7 +3099,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3118,14 +3110,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3138,25 +3130,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3205,7 +3197,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3217,7 +3209,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3229,7 +3221,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3240,10 +3232,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3263,20 +3255,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3325,7 +3317,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3337,22 +3329,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3360,14 +3352,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3383,20 +3375,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3445,7 +3437,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3457,19 +3449,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3480,14 +3472,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3503,19 +3495,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3565,7 +3557,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3577,19 +3569,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3600,10 +3592,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3611,34 +3603,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="J14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3663,58 +3655,58 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3722,10 +3714,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3748,19 +3740,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3785,13 +3777,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3809,7 +3801,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3821,7 +3813,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3833,10 +3825,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3844,45 +3836,45 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3907,67 +3899,67 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3978,7 +3970,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3990,13 +3982,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4047,31 +4039,31 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4082,14 +4074,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4108,16 +4100,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4155,19 +4147,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4179,7 +4171,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4191,7 +4183,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4202,10 +4194,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4225,22 +4217,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4289,7 +4281,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4301,7 +4293,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4310,10 +4302,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4324,10 +4316,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4338,31 +4330,31 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4372,70 +4364,70 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="T20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4446,10 +4438,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4457,34 +4449,34 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G21" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K21" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4533,34 +4525,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4568,10 +4560,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4591,19 +4583,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4653,7 +4645,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4665,7 +4657,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4674,13 +4666,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4688,45 +4680,45 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4775,34 +4767,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4810,45 +4802,45 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4885,44 +4877,44 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AF24" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4930,47 +4922,47 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5019,34 +5011,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5054,10 +5046,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5068,28 +5060,28 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K26" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5139,19 +5131,19 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5160,13 +5152,13 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5174,10 +5166,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5185,7 +5177,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>81</v>
@@ -5197,20 +5189,20 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5259,7 +5251,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5271,22 +5263,22 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5294,10 +5286,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5305,34 +5297,34 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5369,92 +5361,92 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K29" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5503,45 +5495,45 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5552,7 +5544,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5564,13 +5556,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5621,31 +5613,31 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5656,14 +5648,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5682,16 +5674,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5729,19 +5721,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AC31" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AC31" t="s" s="2">
+      <c r="AD31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE31" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AD31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE31" t="s" s="2">
+      <c r="AF31" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5753,7 +5745,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5765,7 +5757,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5776,10 +5768,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5787,34 +5779,34 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5863,31 +5855,31 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5898,10 +5890,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5912,102 +5904,104 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q33" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="R33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="P33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="R33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y33" s="2"/>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6018,10 +6012,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6032,29 +6026,29 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6103,31 +6097,31 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6138,10 +6132,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6152,29 +6146,29 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6223,31 +6217,31 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI35" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI35" t="s" s="2">
+      <c r="AJ35" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6258,10 +6252,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6272,31 +6266,31 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6345,31 +6339,31 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6380,10 +6374,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6394,7 +6388,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6406,19 +6400,19 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6443,55 +6437,55 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Y37" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Y37" t="s" s="2">
+      <c r="Z37" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI37" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI37" t="s" s="2">
+      <c r="AJ37" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6502,14 +6496,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6528,19 +6522,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6565,14 +6559,14 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6589,7 +6583,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6601,33 +6595,33 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6641,7 +6635,7 @@
         <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6650,19 +6644,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6711,7 +6705,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6723,7 +6717,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6732,10 +6726,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6746,10 +6740,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6760,7 +6754,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6772,16 +6766,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6807,69 +6801,69 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Z40" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z40" t="s" s="2">
+      <c r="AA40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AA40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6880,7 +6874,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6892,19 +6886,19 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6929,55 +6923,55 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="Z41" t="s" s="2">
+      <c r="AA41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AA41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6988,10 +6982,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7002,7 +6996,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7014,16 +7008,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7073,45 +7067,45 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7122,7 +7116,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7134,16 +7128,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7193,45 +7187,45 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7254,19 +7248,19 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7315,7 +7309,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7327,19 +7321,19 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AK44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7350,10 +7344,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7364,7 +7358,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7376,13 +7370,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7433,31 +7427,31 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7468,14 +7462,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7494,16 +7488,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7553,7 +7547,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7565,7 +7559,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7577,7 +7571,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7588,14 +7582,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7608,25 +7602,25 @@
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7675,7 +7669,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7687,7 +7681,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7699,7 +7693,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7710,10 +7704,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7724,7 +7718,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7736,13 +7730,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7793,31 +7787,31 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7828,10 +7822,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7842,7 +7836,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7854,13 +7848,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7911,31 +7905,31 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7946,10 +7940,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7960,7 +7954,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7972,19 +7966,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8009,55 +8003,55 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AN50" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8068,10 +8062,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8094,19 +8088,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8131,14 +8125,14 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>474</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8155,7 +8149,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8167,19 +8161,19 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AN51" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8190,10 +8184,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8204,7 +8198,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8216,17 +8210,17 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8275,19 +8269,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8299,7 +8293,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8310,10 +8304,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8324,7 +8318,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8336,13 +8330,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8393,19 +8387,19 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8414,10 +8408,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8428,10 +8422,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8451,19 +8445,19 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8513,7 +8507,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8525,7 +8519,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8534,10 +8528,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8548,10 +8542,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8559,31 +8553,31 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J55" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G55" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K55" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8633,7 +8627,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8645,7 +8639,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8654,10 +8648,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8668,10 +8662,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8691,22 +8685,22 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8755,7 +8749,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8767,19 +8761,19 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8790,10 +8784,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8804,7 +8798,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8816,13 +8810,13 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8873,31 +8867,31 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8908,14 +8902,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8934,16 +8928,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8993,7 +8987,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9005,7 +8999,7 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9017,7 +9011,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9028,14 +9022,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9048,25 +9042,25 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9115,7 +9109,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9127,7 +9121,7 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9139,7 +9133,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9150,10 +9144,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9161,34 +9155,34 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J60" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K60" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="O60" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9213,58 +9207,58 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>515</v>
-      </c>
       <c r="AM60" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9272,10 +9266,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9286,31 +9280,31 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J61" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K61" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9359,45 +9353,45 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9408,7 +9402,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9420,19 +9414,19 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="O62" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9457,55 +9451,55 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Y62" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Y62" t="s" s="2">
+      <c r="Z62" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="Z62" t="s" s="2">
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI62" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AA62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI62" t="s" s="2">
+      <c r="AJ62" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9516,14 +9510,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9542,19 +9536,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9579,14 +9573,14 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9603,7 +9597,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9615,33 +9609,33 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9667,16 +9661,16 @@
         <v>83</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="N64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9725,7 +9719,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9737,7 +9731,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9746,10 +9740,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="571">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:35:55+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -240,16 +240,16 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
     <t>Mapping: SNOMED CT Concept Domain Binding</t>
   </si>
   <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
@@ -284,13 +284,16 @@
     <t>Event</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity|</t>
   </si>
   <si>
     <t>OBX</t>
   </si>
   <si>
-    <t>Observation[classCode=OBS, moodCode=EVN]</t>
+    <t>Entity, Role, or Act,Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -312,7 +315,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -351,7 +354,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -373,13 +376,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -402,10 +405,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -425,13 +432,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -451,7 +462,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -470,11 +481,11 @@
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -499,13 +510,35 @@
     <t>Event.identifier</t>
   </si>
   <si>
-    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>OBX-21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 3) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>FiveWs.identifier</t>
+    <t>Observation.instantiates[x]</t>
+  </si>
+  <si>
+    <t>canonical(ObservationDefinition)
+Reference(ObservationDefinition)</t>
+  </si>
+  <si>
+    <t>Instantiates FHIR ObservationDefinition</t>
+  </si>
+  <si>
+    <t>The reference to a FHIR ObservationDefinition resource that provides the definition that is adhered to in whole or in part by this Observation instance.</t>
+  </si>
+  <si>
+    <t>ObservationDefinition can be referenced by its canonical url using instantiatesCanonical, or by a name or an identifier using the appropriate sub-elements of instantiatesReference.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
   </si>
   <si>
     <t>Observation.basedOn</t>
@@ -537,6 +570,115 @@
     <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
   </si>
   <si>
+    <t>Observation.triggeredBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Triggering observation(s)</t>
+  </si>
+  <si>
+    <t>Identifies the observation(s) that triggered the performance of this observation.</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Observation)
+</t>
+  </si>
+  <si>
+    <t>Triggering observation</t>
+  </si>
+  <si>
+    <t>Reference to the triggering observation.</t>
+  </si>
+  <si>
+    <t>outBoundRelationship</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.type</t>
+  </si>
+  <si>
+    <t>reflex | repeat | re-run</t>
+  </si>
+  <si>
+    <t>The type of trigger.
+Reflex | Repeat | Re-run.</t>
+  </si>
+  <si>
+    <t>The type of TriggeredBy Observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-triggeredbytype|5.0.0</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.reason</t>
+  </si>
+  <si>
+    <t>Reason that the observation was triggered</t>
+  </si>
+  <si>
+    <t>Provides the reason why this observation was performed as a result of the observation(s) referenced.</t>
+  </si>
+  <si>
+    <t>annotation</t>
+  </si>
+  <si>
     <t>Observation.partOf</t>
   </si>
   <si>
@@ -544,7 +686,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy|GenomicStudy)
 </t>
   </si>
   <si>
@@ -554,7 +696,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R5/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -581,18 +723,18 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|5.0.0</t>
   </si>
   <si>
     <t>Event.status</t>
   </si>
   <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
     <t>&lt; 445584004 |Report by finality status|</t>
   </si>
   <si>
@@ -600,9 +742,6 @@
   </si>
   <si>
     <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -624,16 +763,19 @@
     <t>Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
+    <t>preferred</t>
+  </si>
+  <si>
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -658,47 +800,29 @@
     <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
+    <t xml:space="preserve">obs-7
+</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
     <t>OBX-3</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -711,9 +835,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.code.coding</t>
   </si>
   <si>
@@ -772,17 +893,17 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance|BiologicallyDerivedProduct|NutritionProduct)
 </t>
   </si>
   <si>
     <t>Who and/or what the observation is about</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
-  </si>
-  <si>
-    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
+    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+  </si>
+  <si>
+    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
   </si>
   <si>
     <t>Observations have no value if you don't know who or what they're about.</t>
@@ -791,13 +912,13 @@
     <t>Event.subject</t>
   </si>
   <si>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
     <t>PID-3</t>
   </si>
   <si>
     <t>participation[typeCode=RTGT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -813,7 +934,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [http://hl7.org/fhir/StructureDefinition/observation-focusCode](http://hl7.org/fhir/extensions/StructureDefinition-observation-focusCode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -842,16 +963,16 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
-    <t>Event.context</t>
+    <t>Event.encounter</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
   </si>
   <si>
     <t>PV1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
   </si>
   <si>
     <t>Observation.effective[x]</t>
@@ -871,7 +992,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R5/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -887,13 +1008,13 @@
     <t>Event.occurrence[x]</t>
   </si>
   <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
     <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
   </si>
   <si>
     <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
   </si>
   <si>
     <t>Observation.effective[x]:effectiveDateTime</t>
@@ -915,16 +1036,16 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+    <t>For Observations that don't require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R5/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn't require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>OBR-22 (or MSH-7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
     <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -946,13 +1067,13 @@
     <t>Event.performer.actor</t>
   </si>
   <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>OBX-15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
   </si>
   <si>
     <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -968,20 +1089,28 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>- An observation may have:
+  1.  a single value here
+  1.  both a value and a set of related or component values
+  1.  only a set of related or component values.
+-  If a value is present, the datatype for this element should be determined by the `code`.
+-  *CodeableConcept* with just a text would be used instead of a string if the field was usually coded, or if the type associated with the `code` defines a coded value.
+-  *Attachment* is used if the observation result value is a binary file such as an image.  If the observation result value is derived from the binary file (for example 'X' detected and here is the the proof in this image), the binary file may be directly represented using *DocumentReference* and referenced by `derivedFrom`.
+- The usage of valueReference is restricted to the MolecularSequence resource when used as a definitional resource, not as a patient-specific finding. .
+- For additional guidance, see the [Notes section](http://hl7.org/fhir/R5/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t xml:space="preserve">obs-7
-</t>
+    <t>obs-7
+obs-6</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>OBX.2, OBX.5, OBX.6</t>
+    <t>OBX-2, OBX-5, OBX-6</t>
   </si>
   <si>
     <t>value</t>
@@ -1045,7 +1174,7 @@
     <t>Observation.value[x].comparator</t>
   </si>
   <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt; | &lt;= | &gt;= | &gt; | ad - how to understand the value</t>
   </si>
   <si>
     <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -1060,7 +1189,7 @@
     <t>How the Quantity should be understood and represented.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|5.0.0</t>
   </si>
   <si>
     <t>Quantity.comparator</t>
@@ -1184,7 +1313,7 @@
 </t>
   </si>
   <si>
-    <t>High, low, normal, etc.</t>
+    <t>High, low, normal, etc</t>
   </si>
   <si>
     <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
@@ -1233,7 +1362,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
+    <t>NTE-3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
   </si>
   <si>
     <t>subjectOf.observationEvent[code="annotation"].value</t>
@@ -1248,19 +1377,22 @@
     <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
   </si>
   <si>
-    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t xml:space="preserve">obs-8
+</t>
+  </si>
+  <si>
     <t>&lt; 123037004 |Body structure|</t>
   </si>
   <si>
@@ -1273,6 +1405,22 @@
     <t>718497002 |Inherent location|</t>
   </si>
   <si>
+    <t>Observation.bodyStructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(BodyStructure)
+</t>
+  </si>
+  <si>
+    <t>Observed body structure</t>
+  </si>
+  <si>
+    <t>Indicates the body structure on the subject's body where the observation was made (i.e. the target site).</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code found in Observation.code or bodySite is used. In many systems, this may be represented as a related observation instead of an inline component.</t>
+  </si>
+  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1303,7 +1451,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|Group)
 </t>
   </si>
   <si>
@@ -1314,6 +1462,10 @@
   </si>
   <si>
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+obs-9:If Observation.specimen is a reference to Group, the group can only have specimens {(reference.resolve().exists() and reference.resolve() is Group) implies reference.resolve().member.entity.resolve().all($this is Specimen)}</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -1335,10 +1487,10 @@
 </t>
   </si>
   <si>
-    <t>(Measurement) Device</t>
-  </si>
-  <si>
-    <t>The device used to generate the observation data.</t>
+    <t>A reference to the device that generates the measurements or the device settings for the device</t>
+  </si>
+  <si>
+    <t>A reference to the device that generates the measurements or the device settings for the device.</t>
   </si>
   <si>
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
@@ -1357,10 +1509,6 @@
   </si>
   <si>
     <t>Observation.referenceRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
   </si>
   <si>
     <t>Provides guide for interpretation</t>
@@ -1379,7 +1527,7 @@
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
-    <t>OBX.7</t>
+    <t>OBX-7</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=REFV]/target[classCode=OBS, moodCode=EVN]</t>
@@ -1392,20 +1540,6 @@
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
     <t>Observation.referenceRange.low</t>
@@ -1425,9 +1559,6 @@
 </t>
   </si>
   <si>
-    <t>OBX-7</t>
-  </si>
-  <si>
     <t>value:IVL_PQ.low</t>
   </si>
   <si>
@@ -1441,6 +1572,24 @@
   </si>
   <si>
     <t>value:IVL_PQ.high</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.normalValue</t>
+  </si>
+  <si>
+    <t>Normal value, if relevant</t>
+  </si>
+  <si>
+    <t>The value of the normal value of the reference range.</t>
+  </si>
+  <si>
+    <t>Codes identifying the normal value of the observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-referencerange-normalvalue</t>
+  </si>
+  <si>
+    <t>value:IVL_PQ.normal</t>
   </si>
   <si>
     <t>Observation.referenceRange.type</t>
@@ -1519,6 +1668,10 @@
     <t>Observation.referenceRange.text</t>
   </si>
   <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
     <t>Text based reference range in an observation</t>
   </si>
   <si>
@@ -1541,29 +1694,26 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R5/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R5/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
   </si>
   <si>
-    <t>outBoundRelationship</t>
-  </si>
-  <si>
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|ImagingSelection|QuestionnaireResponse|Observation|MolecularSequence|GenomicStudy)
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
+    <t>Related resource from which the observation is made</t>
   </si>
   <si>
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R5/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1578,7 +1728,7 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R5/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
@@ -1625,13 +1775,22 @@
   </si>
   <si>
     <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriodAttachmentReference(MolecularSequence)</t>
   </si>
   <si>
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations:
+-  An observation may have both a value (e.g. an  Apgar score) and component observations (the observations from which the Apgar score was derived). 
+-  If a value is present, the datatype for this element should be determined by the `code`.
+-  *CodeableConcept* with just a text would be used instead of a string if the field was usually coded, or if the type associated with the `code` defines a coded value.
+-  *Attachment* is used if the observation result value is a binary file such as an image.  If the observation result value is derived from the binary file (for example 'X' detected and here is the the proof in this image), the binary file may be directly represented using *DocumentReference* and referenced by `derivedFrom`.
+- If a value is present, the datatype for this element should be determined by the `code`.
+-  *CodeableConcept* with just a text would be used instead of a string if the field was usually coded, or if the type associated with the `code` defines a coded value.
+-  *Attachment* is used if the observation result value is a binary file such as an image.  If the observation result value is derived from the binary file (for example 'X' detected and here is the the proof in this image), the binary file may be directly represented using *DocumentReference* and referenced by `derivedFrom`.
+- The usage of valueReference is restricted to the MolecularSequence resource when used as a definitional resource, not as a patient-specific finding. .
+- For additional guidance, see the [Notes section](http://hl7.org/fhir/R5/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -1808,7 +1967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1895,77 +2054,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -1976,7 +2143,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP64"/>
+  <dimension ref="A1:AP74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
@@ -1989,7 +2156,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.11328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="135.15234375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2004,7 +2171,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.8984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.02734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2015,10 +2182,10 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2264,7 +2431,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2272,10 +2439,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2286,7 +2453,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>82</v>
@@ -2295,19 +2462,19 @@
         <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2357,13 +2524,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2392,10 +2559,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2406,7 +2573,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>82</v>
@@ -2415,16 +2582,16 @@
         <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2475,19 +2642,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2510,10 +2677,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2524,28 +2691,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2595,19 +2762,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2630,10 +2797,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2644,7 +2811,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2656,16 +2823,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2691,13 +2858,13 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>82</v>
@@ -2715,19 +2882,19 @@
         <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2750,21 +2917,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2776,16 +2943,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2835,19 +3002,19 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
@@ -2859,10 +3026,10 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>82</v>
@@ -2870,14 +3037,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2896,16 +3063,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2955,7 +3122,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2964,7 +3131,7 @@
         <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>82</v>
@@ -2979,10 +3146,10 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>82</v>
@@ -2990,14 +3157,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3016,16 +3183,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3075,7 +3242,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3087,7 +3254,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -3099,10 +3266,10 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>82</v>
@@ -3110,14 +3277,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3130,25 +3297,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3197,7 +3364,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3209,7 +3376,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3221,10 +3388,10 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>82</v>
@@ -3232,10 +3399,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3255,20 +3422,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3317,7 +3484,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3329,22 +3496,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3352,21 +3519,21 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3375,21 +3542,21 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3437,34 +3604,34 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3472,14 +3639,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3495,21 +3662,21 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="O13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3557,7 +3724,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3569,22 +3736,22 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>175</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>82</v>
@@ -3592,10 +3759,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3603,35 +3770,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O14" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3655,13 +3818,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3679,34 +3842,34 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3714,10 +3877,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3728,7 +3891,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3740,20 +3903,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3777,13 +3936,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3801,19 +3960,19 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3825,10 +3984,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3836,21 +3995,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3859,23 +4018,21 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3899,11 +4056,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3921,77 +4080,81 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>213</v>
+        <v>141</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -4039,19 +4202,19 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -4063,10 +4226,10 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4074,21 +4237,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4097,20 +4260,18 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4147,31 +4308,31 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4183,10 +4344,10 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4194,10 +4355,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4205,10 +4366,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4217,23 +4378,19 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4257,13 +4414,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4281,19 +4438,19 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4302,13 +4459,13 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4316,10 +4473,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4330,7 +4487,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4339,23 +4496,19 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4364,7 +4517,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>238</v>
+        <v>82</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4403,19 +4556,19 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4424,13 +4577,13 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4438,21 +4591,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4461,23 +4614,21 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4525,34 +4676,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4560,10 +4711,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4571,33 +4722,35 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4621,13 +4774,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4645,34 +4798,34 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4680,21 +4833,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4703,22 +4856,22 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4743,13 +4896,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4767,34 +4920,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>241</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4802,21 +4955,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4825,22 +4978,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4865,80 +5018,78 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>281</v>
+        <v>206</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4947,23 +5098,19 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>271</v>
+        <v>95</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>183</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5011,34 +5158,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>185</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5046,21 +5193,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5069,19 +5216,19 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>285</v>
+        <v>141</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>142</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>288</v>
+        <v>144</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5119,31 +5266,31 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>190</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5152,13 +5299,13 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>291</v>
+        <v>187</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5166,10 +5313,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5177,7 +5324,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>81</v>
@@ -5189,20 +5336,22 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5251,7 +5400,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5263,22 +5412,22 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5286,10 +5435,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5297,10 +5446,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5309,22 +5458,22 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>302</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5334,7 +5483,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5361,68 +5510,68 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AC28" s="2"/>
-      <c r="AD28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE28" t="s" s="2">
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AF28" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5431,22 +5580,22 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5495,45 +5644,45 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5544,7 +5693,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5553,18 +5702,20 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>213</v>
+        <v>290</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>291</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5613,34 +5764,34 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5648,21 +5799,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5671,21 +5822,23 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>138</v>
+        <v>297</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>139</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>219</v>
+        <v>299</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5721,46 +5874,46 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>223</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>217</v>
+        <v>304</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5768,21 +5921,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5791,22 +5944,22 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5843,46 +5996,44 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5890,121 +6041,123 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="J33" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q33" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="R33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6012,10 +6165,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6026,7 +6179,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6035,21 +6188,21 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>213</v>
+        <v>322</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6097,34 +6250,34 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6132,10 +6285,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6143,10 +6296,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6155,20 +6308,20 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>106</v>
+        <v>330</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6217,34 +6370,34 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6252,10 +6405,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6263,10 +6416,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6275,22 +6428,22 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>112</v>
+        <v>339</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6327,31 +6480,29 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6363,32 +6514,34 @@
         <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6397,22 +6550,22 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>190</v>
+        <v>339</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6437,13 +6590,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6461,19 +6614,19 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6482,35 +6635,35 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>135</v>
+        <v>345</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6522,20 +6675,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>375</v>
+        <v>183</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6559,13 +6708,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6583,49 +6732,49 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>373</v>
+        <v>185</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6635,7 +6784,7 @@
         <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6644,20 +6793,18 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>386</v>
+        <v>141</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>387</v>
+        <v>142</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>388</v>
+        <v>189</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6693,19 +6840,19 @@
         <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>385</v>
+        <v>190</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6717,7 +6864,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6726,13 +6873,13 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6740,10 +6887,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6751,10 +6898,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6763,21 +6910,23 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>190</v>
+        <v>357</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6801,13 +6950,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6825,45 +6974,45 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>402</v>
+        <v>363</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6874,36 +7023,36 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q41" s="2"/>
+      <c r="Q41" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="R41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6923,13 +7072,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>397</v>
+        <v>117</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>409</v>
+        <v>371</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6947,19 +7096,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6968,13 +7117,13 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6982,10 +7131,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6996,7 +7145,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7005,21 +7154,21 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>414</v>
+        <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>415</v>
+        <v>378</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7067,45 +7216,45 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>420</v>
+        <v>382</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7116,7 +7265,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7125,21 +7274,21 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>423</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>424</v>
+        <v>386</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7187,45 +7336,45 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>429</v>
+        <v>382</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7236,7 +7385,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7245,22 +7394,22 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>432</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>433</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>434</v>
+        <v>395</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>435</v>
+        <v>396</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>436</v>
+        <v>397</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7309,19 +7458,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>437</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7330,13 +7479,13 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>439</v>
+        <v>382</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7344,10 +7493,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7358,7 +7507,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7370,16 +7519,20 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>214</v>
+        <v>401</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7403,13 +7556,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7427,19 +7580,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>216</v>
+        <v>400</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7451,10 +7604,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7462,14 +7615,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>137</v>
+        <v>411</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7488,18 +7641,20 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>139</v>
+        <v>412</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>219</v>
+        <v>413</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7523,13 +7678,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7547,7 +7702,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>410</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7559,7 +7714,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7568,28 +7723,28 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>217</v>
+        <v>419</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7599,28 +7754,28 @@
         <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>138</v>
+        <v>423</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>141</v>
+        <v>426</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>147</v>
+        <v>427</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7669,7 +7824,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7681,7 +7836,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7693,10 +7848,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>135</v>
+        <v>428</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7704,10 +7859,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7718,7 +7873,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7730,15 +7885,17 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>448</v>
+        <v>233</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7763,13 +7920,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7787,19 +7944,19 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7808,24 +7965,24 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7836,7 +7993,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7848,15 +8005,17 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7905,19 +8064,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7926,13 +8085,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7940,10 +8099,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7954,7 +8113,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7966,19 +8125,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8003,13 +8162,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>116</v>
+        <v>434</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8027,34 +8186,34 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8062,10 +8221,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8076,7 +8235,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8088,20 +8247,18 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>190</v>
+        <v>457</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8125,13 +8282,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8149,45 +8306,45 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>461</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8198,7 +8355,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8210,18 +8367,18 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8269,45 +8426,45 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8318,7 +8475,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8330,16 +8487,20 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8387,20 +8548,20 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>104</v>
-      </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8408,13 +8569,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8422,10 +8583,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8436,7 +8597,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8445,20 +8606,18 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>485</v>
+        <v>182</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>486</v>
+        <v>183</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8507,19 +8666,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>484</v>
+        <v>185</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8528,13 +8687,13 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8542,21 +8701,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8565,19 +8724,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>492</v>
+        <v>141</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>493</v>
+        <v>142</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>494</v>
+        <v>189</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>495</v>
+        <v>144</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8627,7 +8786,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>491</v>
+        <v>190</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8639,7 +8798,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8648,13 +8807,13 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8662,14 +8821,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8682,25 +8841,25 @@
         <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>432</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>498</v>
+        <v>193</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>499</v>
+        <v>194</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>500</v>
+        <v>144</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>501</v>
+        <v>150</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8749,7 +8908,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>497</v>
+        <v>195</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8761,7 +8920,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8770,13 +8929,13 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8784,10 +8943,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8798,7 +8957,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8810,13 +8969,13 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>213</v>
+        <v>487</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>214</v>
+        <v>488</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>489</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8867,19 +9026,19 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>216</v>
+        <v>486</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -8891,10 +9050,10 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>217</v>
+        <v>481</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8902,21 +9061,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -8928,17 +9087,15 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>138</v>
+        <v>487</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>139</v>
+        <v>493</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8987,19 +9144,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>223</v>
+        <v>492</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9011,10 +9168,10 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>217</v>
+        <v>481</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9022,46 +9179,42 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>444</v>
+        <v>497</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9085,13 +9238,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9109,19 +9262,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9133,10 +9286,10 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>135</v>
+        <v>481</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9144,10 +9297,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9155,10 +9308,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9167,22 +9320,22 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>204</v>
+        <v>506</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9207,13 +9360,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>397</v>
+        <v>238</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9231,34 +9384,34 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>208</v>
+        <v>509</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>209</v>
+        <v>510</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9266,10 +9419,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9280,7 +9433,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9289,22 +9442,22 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9329,13 +9482,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9353,45 +9506,45 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>309</v>
+        <v>509</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>310</v>
+        <v>510</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9402,7 +9555,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9414,7 +9567,7 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>190</v>
+        <v>519</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>520</v>
@@ -9422,11 +9575,9 @@
       <c r="M62" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9451,13 +9602,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9475,19 +9626,19 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9496,13 +9647,13 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -9510,21 +9661,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9536,20 +9687,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>190</v>
+        <v>525</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>375</v>
+        <v>526</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9573,13 +9720,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9597,45 +9744,45 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>383</v>
+        <v>481</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9655,23 +9802,21 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9719,7 +9864,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9731,7 +9876,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9740,20 +9885,1232 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>439</v>
+        <v>534</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP64">
+  <autoFilter ref="A1:AP74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9763,7 +11120,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/viral-load-test-result-absolute-decimal</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/viral-load-test-result-absolute-decimal</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -2171,7 +2171,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.02734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="104.1796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/viral-load-test-result-absolute-decimal</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/viral-load-test-result-absolute-decimal</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-vl-result-code</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -2171,7 +2171,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="104.1796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.02734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/viral-load-test-result-absolute-decimal</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/viral-load-test-result-absolute-decimal</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -2171,7 +2171,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.02734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="99.84765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/viral-load-test-result-absolute-decimal</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/viral-load-test-result-absolute-decimal</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-vl-result-code</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -2171,7 +2171,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="99.84765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.02734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
+++ b/StructureDefinition-viral-load-test-result-absolute-decimal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:13:26+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
